--- a/public/data/db-source/variable.xlsx
+++ b/public/data/db-source/variable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bassim/code/datannur/datannur_dev/public/data/db-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D106170-64C6-6C41-BC72-0B795DFBE49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F004B4BB-CA14-B64C-9513-DA21B6202149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5160" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3103" uniqueCount="2020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3107" uniqueCount="2024">
   <si>
     <t>id</t>
   </si>
@@ -6080,6 +6080,18 @@
   </si>
   <si>
     <t>a_or_b_or_c, oui_non</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>std</t>
   </si>
 </sst>
 </file>
@@ -6150,9 +6162,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B5F79C97-E8B2-3E4B-873D-A9EBE7FF4B08}" name="Tableau1" displayName="Tableau1" ref="A1:O343" totalsRowShown="0">
-  <autoFilter ref="A1:O343" xr:uid="{B5F79C97-E8B2-3E4B-873D-A9EBE7FF4B08}"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B5F79C97-E8B2-3E4B-873D-A9EBE7FF4B08}" name="Tableau1" displayName="Tableau1" ref="A1:S343" totalsRowShown="0">
+  <autoFilter ref="A1:S343" xr:uid="{B5F79C97-E8B2-3E4B-873D-A9EBE7FF4B08}"/>
+  <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{93604F40-CD55-3D4B-AC71-27C6EBB96585}" name="id"/>
     <tableColumn id="2" xr3:uid="{BF843A60-41B0-EA48-977A-51FEEA73F6C7}" name="dataset_id"/>
     <tableColumn id="3" xr3:uid="{BCB7C440-426C-EF4D-8E48-57BB86725760}" name="name"/>
@@ -6168,6 +6180,10 @@
     <tableColumn id="13" xr3:uid="{0D9C543A-3D7D-A74A-A543-90491A90EB94}" name="tag_ids"/>
     <tableColumn id="14" xr3:uid="{80B52D4C-5640-6240-939A-6DC6F1F2147C}" name="key"/>
     <tableColumn id="15" xr3:uid="{8C4309FC-4A37-1243-B760-EBAD68048C78}" name="source_var_ids"/>
+    <tableColumn id="16" xr3:uid="{CB39A0C5-83B2-B24E-A308-ED24274927D2}" name="min"/>
+    <tableColumn id="17" xr3:uid="{0AEBB360-9070-7B43-9CA7-884E075866BF}" name="max"/>
+    <tableColumn id="18" xr3:uid="{C77E4BF0-5715-E048-A147-739835ABF606}" name="mean"/>
+    <tableColumn id="19" xr3:uid="{DCF9CF32-8576-DF40-8B35-DAF22D9C2690}" name="std"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6460,7 +6476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O343"/>
+  <dimension ref="A1:S343"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
@@ -6479,7 +6495,7 @@
     <col min="15" max="15" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6525,8 +6541,20 @@
       <c r="O1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P1" t="s">
+        <v>2020</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>2021</v>
+      </c>
+      <c r="R1" t="s">
+        <v>2022</v>
+      </c>
+      <c r="S1" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -6567,7 +6595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -6608,7 +6636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -6649,7 +6677,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -6687,7 +6715,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -6728,7 +6756,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>56</v>
       </c>
@@ -6766,7 +6794,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -6804,7 +6832,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>64</v>
       </c>
@@ -6842,7 +6870,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>68</v>
       </c>
@@ -6883,7 +6911,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>72</v>
       </c>
@@ -6924,7 +6952,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>76</v>
       </c>
@@ -6962,7 +6990,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>80</v>
       </c>
@@ -7000,7 +7028,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>84</v>
       </c>
@@ -7041,7 +7069,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>88</v>
       </c>
@@ -7076,7 +7104,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>92</v>
       </c>
@@ -7117,7 +7145,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>96</v>
       </c>
@@ -7152,7 +7180,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>100</v>
       </c>
@@ -7189,8 +7217,20 @@
       <c r="M18" t="s">
         <v>1675</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P18">
+        <v>3</v>
+      </c>
+      <c r="Q18">
+        <v>43</v>
+      </c>
+      <c r="R18">
+        <v>17</v>
+      </c>
+      <c r="S18">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>104</v>
       </c>
@@ -7228,7 +7268,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>108</v>
       </c>
@@ -7266,7 +7306,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -7303,8 +7343,20 @@
       <c r="M21" t="s">
         <v>1678</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P21">
+        <v>-202223</v>
+      </c>
+      <c r="Q21">
+        <v>4535435</v>
+      </c>
+      <c r="R21">
+        <v>2343</v>
+      </c>
+      <c r="S21">
+        <v>34.432000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>116</v>
       </c>
@@ -7339,7 +7391,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>121</v>
       </c>
@@ -7377,7 +7429,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -7415,7 +7467,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>129</v>
       </c>
@@ -7456,7 +7508,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>133</v>
       </c>
@@ -7491,7 +7543,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>137</v>
       </c>
@@ -7529,7 +7581,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>139</v>
       </c>
@@ -7570,7 +7622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>143</v>
       </c>
@@ -7617,7 +7669,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>147</v>
       </c>
@@ -7658,7 +7710,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>151</v>
       </c>
@@ -7696,7 +7748,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>155</v>
       </c>

--- a/public/data/db-source/variable.xlsx
+++ b/public/data/db-source/variable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bassim/code/datannur/datannur_dev/public/data/db-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F004B4BB-CA14-B64C-9513-DA21B6202149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3ADC9F9-2AEE-0D48-ACD9-C2C5C494F3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10871,7 +10871,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>456</v>
       </c>
@@ -10909,7 +10909,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>460</v>
       </c>
@@ -10944,7 +10944,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>464</v>
       </c>
@@ -10982,7 +10982,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>468</v>
       </c>
@@ -11020,7 +11020,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>470</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>474</v>
       </c>
@@ -11093,7 +11093,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>478</v>
       </c>
@@ -11127,8 +11127,20 @@
       <c r="M119" t="s">
         <v>1760</v>
       </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P119">
+        <v>1590102632</v>
+      </c>
+      <c r="Q119">
+        <v>1774134632</v>
+      </c>
+      <c r="R119">
+        <v>1726960232</v>
+      </c>
+      <c r="S119">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>483</v>
       </c>
@@ -11166,7 +11178,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>487</v>
       </c>
@@ -11201,7 +11213,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>489</v>
       </c>
@@ -11233,7 +11245,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>493</v>
       </c>
@@ -11268,7 +11280,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>497</v>
       </c>
@@ -11303,7 +11315,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>501</v>
       </c>
@@ -11341,7 +11353,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>505</v>
       </c>
@@ -11376,7 +11388,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>509</v>
       </c>
@@ -11414,7 +11426,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>513</v>
       </c>

--- a/public/data/db-source/variable.xlsx
+++ b/public/data/db-source/variable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bassim/code/datannur/datannur_dev/public/data/db-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3ADC9F9-2AEE-0D48-ACD9-C2C5C494F3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F168F029-3EA1-C140-8B45-DE2F2C8A5211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3107" uniqueCount="2024">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3107" uniqueCount="2025">
   <si>
     <t>id</t>
   </si>
@@ -6092,6 +6092,9 @@
   </si>
   <si>
     <t>std</t>
+  </si>
+  <si>
+    <t>datetime</t>
   </si>
 </sst>
 </file>
@@ -11154,7 +11157,7 @@
         <v>485</v>
       </c>
       <c r="E120" t="s">
-        <v>9</v>
+        <v>2024</v>
       </c>
       <c r="F120">
         <v>24</v>

--- a/public/data/db-source/variable.xlsx
+++ b/public/data/db-source/variable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bassim/code/datannur/datannur_dev/public/data/db-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F168F029-3EA1-C140-8B45-DE2F2C8A5211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B536E4-E379-214A-8639-0AC21A9552F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3107" uniqueCount="2025">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3103" uniqueCount="2026">
   <si>
     <t>id</t>
   </si>
@@ -6095,6 +6095,9 @@
   </si>
   <si>
     <t>datetime</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
@@ -10925,9 +10928,6 @@
       <c r="D114" t="s">
         <v>462</v>
       </c>
-      <c r="E114" t="s">
-        <v>9</v>
-      </c>
       <c r="F114">
         <v>10</v>
       </c>
@@ -11880,9 +11880,6 @@
       <c r="D140" t="s">
         <v>562</v>
       </c>
-      <c r="E140" t="s">
-        <v>9</v>
-      </c>
       <c r="F140" s="2">
         <v>2300</v>
       </c>
@@ -11915,9 +11912,6 @@
       <c r="D141" t="s">
         <v>566</v>
       </c>
-      <c r="E141" t="s">
-        <v>8</v>
-      </c>
       <c r="F141">
         <v>300</v>
       </c>
@@ -11953,9 +11947,6 @@
       <c r="D142" t="s">
         <v>570</v>
       </c>
-      <c r="E142" t="s">
-        <v>54</v>
-      </c>
       <c r="F142" s="2">
         <v>2000</v>
       </c>
@@ -16479,7 +16470,7 @@
         <v>679</v>
       </c>
       <c r="E261" t="s">
-        <v>9</v>
+        <v>2025</v>
       </c>
       <c r="F261">
         <v>60</v>

--- a/public/data/db-source/variable.xlsx
+++ b/public/data/db-source/variable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bassim/code/datannur/datannur_dev/public/data/db-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B536E4-E379-214A-8639-0AC21A9552F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34178825-C5D0-5B4A-9A70-24018A376B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3103" uniqueCount="2026">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3106" uniqueCount="2028">
   <si>
     <t>id</t>
   </si>
@@ -6098,6 +6098,12 @@
   </si>
   <si>
     <t>test</t>
+  </si>
+  <si>
+    <t>fk_var_id</t>
+  </si>
+  <si>
+    <t>pop_region__regionfake</t>
   </si>
 </sst>
 </file>
@@ -6147,7 +6153,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
@@ -6168,9 +6177,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B5F79C97-E8B2-3E4B-873D-A9EBE7FF4B08}" name="Tableau1" displayName="Tableau1" ref="A1:S343" totalsRowShown="0">
-  <autoFilter ref="A1:S343" xr:uid="{B5F79C97-E8B2-3E4B-873D-A9EBE7FF4B08}"/>
-  <tableColumns count="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B5F79C97-E8B2-3E4B-873D-A9EBE7FF4B08}" name="Tableau1" displayName="Tableau1" ref="A1:T343" totalsRowShown="0">
+  <autoFilter ref="A1:T343" xr:uid="{B5F79C97-E8B2-3E4B-873D-A9EBE7FF4B08}"/>
+  <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{93604F40-CD55-3D4B-AC71-27C6EBB96585}" name="id"/>
     <tableColumn id="2" xr3:uid="{BF843A60-41B0-EA48-977A-51FEEA73F6C7}" name="dataset_id"/>
     <tableColumn id="3" xr3:uid="{BCB7C440-426C-EF4D-8E48-57BB86725760}" name="name"/>
@@ -6180,8 +6189,9 @@
     <tableColumn id="6" xr3:uid="{2AD67B87-951A-4040-9E30-7B869046BA77}" name="nb_duplicate"/>
     <tableColumn id="7" xr3:uid="{93481DF3-DBA0-D743-9503-D16273046754}" name="nb_missing"/>
     <tableColumn id="8" xr3:uid="{FD4B4D3E-8867-AA4D-9093-A135708498A9}" name="description"/>
-    <tableColumn id="9" xr3:uid="{0DB3AD0D-30A6-B443-92FF-88F6E231297E}" name="start_date" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{7AEC9287-EE71-324F-90D8-FD7C1B573F48}" name="end_date" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{0DB3AD0D-30A6-B443-92FF-88F6E231297E}" name="start_date" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{7AEC9287-EE71-324F-90D8-FD7C1B573F48}" name="end_date" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{47C050EA-B750-8349-B07C-CEEF3EBF978F}" name="fk_var_id" dataDxfId="0"/>
     <tableColumn id="12" xr3:uid="{113E5C5D-89D6-9C42-8737-7B27E528F557}" name="modality_ids"/>
     <tableColumn id="13" xr3:uid="{0D9C543A-3D7D-A74A-A543-90491A90EB94}" name="tag_ids"/>
     <tableColumn id="14" xr3:uid="{80B52D4C-5640-6240-939A-6DC6F1F2147C}" name="key"/>
@@ -6482,7 +6492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S343"/>
+  <dimension ref="A1:T343"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
@@ -6496,12 +6506,13 @@
     <col min="9" max="9" width="32.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.33203125" customWidth="1"/>
+    <col min="12" max="12" width="11" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6535,32 +6546,35 @@
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>2026</v>
+      </c>
+      <c r="M1" t="s">
         <v>26</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>31</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>33</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>34</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>2020</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>2021</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>2022</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>2023</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -6594,14 +6608,14 @@
       <c r="K2" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>1663</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -6635,14 +6649,14 @@
       <c r="K3" s="1" t="s">
         <v>1273</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>1664</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -6676,14 +6690,14 @@
       <c r="K4" s="1" t="s">
         <v>1275</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>1665</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -6717,11 +6731,11 @@
       <c r="K5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>1666</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -6755,14 +6769,14 @@
       <c r="K6" s="1" t="s">
         <v>1278</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>1667</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>1935</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>56</v>
       </c>
@@ -6796,11 +6810,11 @@
       <c r="K7" s="1" t="s">
         <v>1280</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>1668</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -6834,11 +6848,11 @@
       <c r="K8" s="1" t="s">
         <v>1281</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>2000</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>64</v>
       </c>
@@ -6872,11 +6886,11 @@
       <c r="K9" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>2001</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>68</v>
       </c>
@@ -6911,13 +6925,16 @@
         <v>1284</v>
       </c>
       <c r="L10" t="s">
+        <v>2027</v>
+      </c>
+      <c r="M10" t="s">
         <v>27</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>1669</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>72</v>
       </c>
@@ -6951,14 +6968,14 @@
       <c r="K11" s="1" t="s">
         <v>1286</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>2002</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>1670</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>76</v>
       </c>
@@ -6992,11 +7009,11 @@
       <c r="K12" s="1" t="s">
         <v>1287</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>1671</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>80</v>
       </c>
@@ -7030,11 +7047,11 @@
       <c r="K13" s="1" t="s">
         <v>1289</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>1672</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>84</v>
       </c>
@@ -7068,14 +7085,14 @@
       <c r="K14" s="1" t="s">
         <v>1291</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>2003</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>1673</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>88</v>
       </c>
@@ -7110,7 +7127,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>92</v>
       </c>
@@ -7144,14 +7161,14 @@
       <c r="K16" s="1" t="s">
         <v>1295</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>1674</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>1936</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>96</v>
       </c>
@@ -7186,7 +7203,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>100</v>
       </c>
@@ -7220,23 +7237,23 @@
       <c r="K18" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>1675</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>3</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>43</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>17</v>
       </c>
-      <c r="S18">
+      <c r="T18">
         <v>0.32</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>104</v>
       </c>
@@ -7270,11 +7287,11 @@
       <c r="K19" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>1676</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>108</v>
       </c>
@@ -7308,11 +7325,11 @@
       <c r="K20" s="1" t="s">
         <v>1301</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>1677</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -7346,23 +7363,23 @@
       <c r="K21" s="1" t="s">
         <v>1303</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>1678</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>-202223</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>4535435</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <v>2343</v>
       </c>
-      <c r="S21">
+      <c r="T21">
         <v>34.432000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>116</v>
       </c>
@@ -7397,7 +7414,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>121</v>
       </c>
@@ -7431,11 +7448,11 @@
       <c r="K23" s="1" t="s">
         <v>1307</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>1679</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -7469,11 +7486,11 @@
       <c r="K24" s="1" t="s">
         <v>1309</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
         <v>1680</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>129</v>
       </c>
@@ -7507,14 +7524,14 @@
       <c r="K25" s="1" t="s">
         <v>1311</v>
       </c>
-      <c r="M25" t="s">
+      <c r="N25" t="s">
         <v>1681</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>133</v>
       </c>
@@ -7549,7 +7566,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>137</v>
       </c>
@@ -7580,14 +7597,14 @@
       <c r="K27" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L27" t="s">
+      <c r="M27" t="s">
         <v>2004</v>
       </c>
-      <c r="M27" t="s">
+      <c r="N27" t="s">
         <v>1682</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>139</v>
       </c>
@@ -7621,14 +7638,17 @@
       <c r="K28" s="1" t="s">
         <v>1314</v>
       </c>
-      <c r="M28" t="s">
+      <c r="L28" t="s">
+        <v>277</v>
+      </c>
+      <c r="N28" t="s">
         <v>1683</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>143</v>
       </c>
@@ -7662,20 +7682,20 @@
       <c r="K29" s="1" t="s">
         <v>1316</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
         <v>2003</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" t="s">
         <v>1684</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>2</v>
       </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>147</v>
       </c>
@@ -7709,14 +7729,14 @@
       <c r="K30" s="1" t="s">
         <v>1318</v>
       </c>
-      <c r="M30" t="s">
+      <c r="N30" t="s">
         <v>1685</v>
       </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>1937</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>151</v>
       </c>
@@ -7750,11 +7770,11 @@
       <c r="K31" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="M31" t="s">
+      <c r="N31" t="s">
         <v>1686</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>155</v>
       </c>
@@ -7785,14 +7805,14 @@
       <c r="J32" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="M32" t="s">
+      <c r="N32" t="s">
         <v>1687</v>
       </c>
-      <c r="O32" t="s">
+      <c r="P32" t="s">
         <v>1057</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>159</v>
       </c>
@@ -7826,11 +7846,11 @@
       <c r="K33" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M33" t="s">
+      <c r="N33" t="s">
         <v>1688</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>163</v>
       </c>
@@ -7864,11 +7884,11 @@
       <c r="K34" s="1" t="s">
         <v>1292</v>
       </c>
-      <c r="M34" t="s">
+      <c r="N34" t="s">
         <v>1689</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>167</v>
       </c>
@@ -7902,11 +7922,11 @@
       <c r="K35" s="1" t="s">
         <v>1325</v>
       </c>
-      <c r="M35" t="s">
+      <c r="N35" t="s">
         <v>1690</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>170</v>
       </c>
@@ -7940,11 +7960,11 @@
       <c r="K36" s="1" t="s">
         <v>1327</v>
       </c>
-      <c r="M36" t="s">
+      <c r="N36" t="s">
         <v>1691</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>174</v>
       </c>
@@ -7978,17 +7998,17 @@
       <c r="K37" s="1" t="s">
         <v>1328</v>
       </c>
-      <c r="L37" t="s">
+      <c r="M37" t="s">
         <v>30</v>
       </c>
-      <c r="M37" t="s">
+      <c r="N37" t="s">
         <v>1692</v>
       </c>
-      <c r="O37" t="s">
+      <c r="P37" t="s">
         <v>1938</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>177</v>
       </c>
@@ -8022,11 +8042,11 @@
       <c r="K38" s="1" t="s">
         <v>1330</v>
       </c>
-      <c r="O38" t="s">
+      <c r="P38" t="s">
         <v>1939</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>181</v>
       </c>
@@ -8060,11 +8080,11 @@
       <c r="K39" s="1" t="s">
         <v>1311</v>
       </c>
-      <c r="M39" t="s">
+      <c r="N39" t="s">
         <v>1693</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>185</v>
       </c>
@@ -8098,11 +8118,11 @@
       <c r="K40" s="1" t="s">
         <v>1333</v>
       </c>
-      <c r="L40" t="s">
+      <c r="M40" t="s">
         <v>2003</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>188</v>
       </c>
@@ -8136,17 +8156,17 @@
       <c r="K41" s="1" t="s">
         <v>1335</v>
       </c>
-      <c r="L41" t="s">
+      <c r="M41" t="s">
         <v>2005</v>
       </c>
-      <c r="M41" t="s">
+      <c r="N41" t="s">
         <v>1694</v>
       </c>
-      <c r="O41" t="s">
+      <c r="P41" t="s">
         <v>1940</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>192</v>
       </c>
@@ -8181,7 +8201,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>196</v>
       </c>
@@ -8215,11 +8235,11 @@
       <c r="K43" s="1" t="s">
         <v>1338</v>
       </c>
-      <c r="M43" t="s">
+      <c r="N43" t="s">
         <v>1695</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>200</v>
       </c>
@@ -8253,14 +8273,14 @@
       <c r="K44" s="1" t="s">
         <v>1340</v>
       </c>
-      <c r="M44" t="s">
+      <c r="N44" t="s">
         <v>1696</v>
       </c>
-      <c r="O44" t="s">
+      <c r="P44" t="s">
         <v>1941</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>204</v>
       </c>
@@ -8291,14 +8311,14 @@
       <c r="J45" s="1" t="s">
         <v>1341</v>
       </c>
-      <c r="M45" t="s">
+      <c r="N45" t="s">
         <v>1697</v>
       </c>
-      <c r="O45" t="s">
+      <c r="P45" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>208</v>
       </c>
@@ -8332,14 +8352,14 @@
       <c r="K46" s="1" t="s">
         <v>1343</v>
       </c>
-      <c r="M46" t="s">
+      <c r="N46" t="s">
         <v>1698</v>
       </c>
-      <c r="O46" t="s">
+      <c r="P46" t="s">
         <v>1942</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>212</v>
       </c>
@@ -8373,11 +8393,11 @@
       <c r="K47" s="1" t="s">
         <v>1274</v>
       </c>
-      <c r="M47" t="s">
+      <c r="N47" t="s">
         <v>1699</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>216</v>
       </c>
@@ -8411,14 +8431,14 @@
       <c r="K48" s="1" t="s">
         <v>1345</v>
       </c>
-      <c r="M48" t="s">
+      <c r="N48" t="s">
         <v>1688</v>
       </c>
-      <c r="O48" t="s">
+      <c r="P48" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>220</v>
       </c>
@@ -8452,17 +8472,17 @@
       <c r="K49" s="1" t="s">
         <v>1347</v>
       </c>
-      <c r="L49" t="s">
+      <c r="M49" t="s">
         <v>30</v>
       </c>
-      <c r="M49" t="s">
+      <c r="N49" t="s">
         <v>1700</v>
       </c>
-      <c r="O49" t="s">
+      <c r="P49" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>224</v>
       </c>
@@ -8496,11 +8516,11 @@
       <c r="K50" s="1" t="s">
         <v>1274</v>
       </c>
-      <c r="M50" t="s">
+      <c r="N50" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>228</v>
       </c>
@@ -8534,11 +8554,11 @@
       <c r="K51" s="1" t="s">
         <v>1350</v>
       </c>
-      <c r="M51" t="s">
+      <c r="N51" t="s">
         <v>1702</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>232</v>
       </c>
@@ -8572,11 +8592,11 @@
       <c r="K52" s="1" t="s">
         <v>1352</v>
       </c>
-      <c r="M52" t="s">
+      <c r="N52" t="s">
         <v>1703</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>236</v>
       </c>
@@ -8611,7 +8631,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>240</v>
       </c>
@@ -8645,14 +8665,14 @@
       <c r="K54" s="1" t="s">
         <v>1356</v>
       </c>
-      <c r="L54" t="s">
+      <c r="M54" t="s">
         <v>30</v>
       </c>
-      <c r="M54" t="s">
+      <c r="N54" t="s">
         <v>1704</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>244</v>
       </c>
@@ -8687,7 +8707,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>248</v>
       </c>
@@ -8721,11 +8741,11 @@
       <c r="K56" s="1" t="s">
         <v>1359</v>
       </c>
-      <c r="M56" t="s">
+      <c r="N56" t="s">
         <v>1705</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>252</v>
       </c>
@@ -8759,11 +8779,11 @@
       <c r="K57" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="M57" t="s">
+      <c r="N57" t="s">
         <v>1706</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>256</v>
       </c>
@@ -8797,11 +8817,11 @@
       <c r="K58" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="M58" t="s">
+      <c r="N58" t="s">
         <v>1707</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>260</v>
       </c>
@@ -8835,11 +8855,11 @@
       <c r="K59" s="1" t="s">
         <v>1362</v>
       </c>
-      <c r="M59" t="s">
+      <c r="N59" t="s">
         <v>1708</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>264</v>
       </c>
@@ -8870,14 +8890,14 @@
       <c r="J60" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L60" t="s">
+      <c r="M60" t="s">
         <v>2004</v>
       </c>
-      <c r="M60" t="s">
+      <c r="N60" t="s">
         <v>1709</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>268</v>
       </c>
@@ -8911,11 +8931,11 @@
       <c r="K61" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M61" t="s">
+      <c r="N61" t="s">
         <v>1710</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>272</v>
       </c>
@@ -8949,14 +8969,14 @@
       <c r="K62" s="1" t="s">
         <v>1365</v>
       </c>
-      <c r="L62" t="s">
+      <c r="M62" t="s">
         <v>2006</v>
       </c>
-      <c r="M62" t="s">
+      <c r="N62" t="s">
         <v>1711</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>275</v>
       </c>
@@ -8990,17 +9010,17 @@
       <c r="K63" s="1" t="s">
         <v>1367</v>
       </c>
-      <c r="L63" t="s">
+      <c r="M63" t="s">
         <v>29</v>
       </c>
-      <c r="M63" t="s">
+      <c r="N63" t="s">
         <v>1712</v>
       </c>
-      <c r="O63" t="s">
+      <c r="P63" t="s">
         <v>1943</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>277</v>
       </c>
@@ -9034,11 +9054,11 @@
       <c r="K64" s="1" t="s">
         <v>1369</v>
       </c>
-      <c r="M64" t="s">
+      <c r="N64" t="s">
         <v>1713</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>279</v>
       </c>
@@ -9072,11 +9092,11 @@
       <c r="K65" s="1" t="s">
         <v>1371</v>
       </c>
-      <c r="M65" t="s">
+      <c r="N65" t="s">
         <v>1714</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>283</v>
       </c>
@@ -9110,11 +9130,11 @@
       <c r="K66" s="1" t="s">
         <v>1372</v>
       </c>
-      <c r="M66" t="s">
+      <c r="N66" t="s">
         <v>1715</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>287</v>
       </c>
@@ -9148,11 +9168,11 @@
       <c r="K67" s="1" t="s">
         <v>1374</v>
       </c>
-      <c r="M67" t="s">
+      <c r="N67" t="s">
         <v>1716</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>291</v>
       </c>
@@ -9186,14 +9206,14 @@
       <c r="K68" s="1" t="s">
         <v>1376</v>
       </c>
-      <c r="M68" t="s">
+      <c r="N68" t="s">
         <v>1717</v>
       </c>
-      <c r="O68" t="s">
+      <c r="P68" t="s">
         <v>1944</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>295</v>
       </c>
@@ -9227,11 +9247,11 @@
       <c r="K69" s="1" t="s">
         <v>1378</v>
       </c>
-      <c r="M69" t="s">
+      <c r="N69" t="s">
         <v>1718</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>299</v>
       </c>
@@ -9265,14 +9285,14 @@
       <c r="K70" s="1" t="s">
         <v>1379</v>
       </c>
-      <c r="M70" t="s">
+      <c r="N70" t="s">
         <v>1719</v>
       </c>
-      <c r="O70" t="s">
+      <c r="P70" t="s">
         <v>1945</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>303</v>
       </c>
@@ -9306,14 +9326,14 @@
       <c r="K71" s="1" t="s">
         <v>1381</v>
       </c>
-      <c r="L71" t="s">
+      <c r="M71" t="s">
         <v>2007</v>
       </c>
-      <c r="M71" t="s">
+      <c r="N71" t="s">
         <v>1720</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>307</v>
       </c>
@@ -9347,11 +9367,11 @@
       <c r="K72" s="1" t="s">
         <v>1383</v>
       </c>
-      <c r="M72" t="s">
+      <c r="N72" t="s">
         <v>1721</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>311</v>
       </c>
@@ -9385,14 +9405,14 @@
       <c r="K73" s="1" t="s">
         <v>1385</v>
       </c>
-      <c r="L73" t="s">
+      <c r="M73" t="s">
         <v>2008</v>
       </c>
-      <c r="M73" t="s">
+      <c r="N73" t="s">
         <v>1722</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>315</v>
       </c>
@@ -9423,11 +9443,11 @@
       <c r="J74" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M74" t="s">
+      <c r="N74" t="s">
         <v>1723</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>319</v>
       </c>
@@ -9461,14 +9481,14 @@
       <c r="K75" s="1" t="s">
         <v>1387</v>
       </c>
-      <c r="L75" t="s">
+      <c r="M75" t="s">
         <v>2009</v>
       </c>
-      <c r="M75" t="s">
+      <c r="N75" t="s">
         <v>1724</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>322</v>
       </c>
@@ -9502,11 +9522,11 @@
       <c r="K76" s="1" t="s">
         <v>1389</v>
       </c>
-      <c r="M76" t="s">
+      <c r="N76" t="s">
         <v>1725</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>326</v>
       </c>
@@ -9541,7 +9561,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>330</v>
       </c>
@@ -9575,11 +9595,11 @@
       <c r="K78" s="1" t="s">
         <v>1393</v>
       </c>
-      <c r="M78" t="s">
+      <c r="N78" t="s">
         <v>1726</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>332</v>
       </c>
@@ -9613,11 +9633,11 @@
       <c r="K79" s="1" t="s">
         <v>1395</v>
       </c>
-      <c r="M79" t="s">
+      <c r="N79" t="s">
         <v>1727</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>335</v>
       </c>
@@ -9652,7 +9672,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>337</v>
       </c>
@@ -9683,14 +9703,14 @@
       <c r="J81" s="1" t="s">
         <v>1396</v>
       </c>
-      <c r="L81" t="s">
+      <c r="M81" t="s">
         <v>2005</v>
       </c>
-      <c r="M81" t="s">
+      <c r="N81" t="s">
         <v>1728</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>341</v>
       </c>
@@ -9724,14 +9744,14 @@
       <c r="K82" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L82" t="s">
+      <c r="M82" t="s">
         <v>2005</v>
       </c>
-      <c r="M82" t="s">
+      <c r="N82" t="s">
         <v>1729</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>345</v>
       </c>
@@ -9765,11 +9785,11 @@
       <c r="K83" s="1" t="s">
         <v>1398</v>
       </c>
-      <c r="M83" t="s">
+      <c r="N83" t="s">
         <v>1730</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>349</v>
       </c>
@@ -9800,14 +9820,14 @@
       <c r="J84" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M84" t="s">
+      <c r="N84" t="s">
         <v>1731</v>
       </c>
-      <c r="O84" t="s">
+      <c r="P84" t="s">
         <v>1946</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>353</v>
       </c>
@@ -9841,14 +9861,14 @@
       <c r="K85" s="1" t="s">
         <v>1399</v>
       </c>
-      <c r="L85" t="s">
+      <c r="M85" t="s">
         <v>2010</v>
       </c>
-      <c r="M85" t="s">
+      <c r="N85" t="s">
         <v>1732</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>357</v>
       </c>
@@ -9882,11 +9902,11 @@
       <c r="K86" s="1" t="s">
         <v>1401</v>
       </c>
-      <c r="M86" t="s">
+      <c r="N86" t="s">
         <v>1733</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>361</v>
       </c>
@@ -9920,11 +9940,11 @@
       <c r="K87" s="1" t="s">
         <v>1403</v>
       </c>
-      <c r="M87" t="s">
+      <c r="N87" t="s">
         <v>1734</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>364</v>
       </c>
@@ -9958,11 +9978,11 @@
       <c r="K88" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="M88" t="s">
+      <c r="N88" t="s">
         <v>1735</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>366</v>
       </c>
@@ -9996,11 +10016,11 @@
       <c r="K89" s="1" t="s">
         <v>1378</v>
       </c>
-      <c r="O89" t="s">
+      <c r="P89" t="s">
         <v>1947</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>368</v>
       </c>
@@ -10034,11 +10054,11 @@
       <c r="K90" s="1" t="s">
         <v>1408</v>
       </c>
-      <c r="M90" t="s">
+      <c r="N90" t="s">
         <v>1736</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>372</v>
       </c>
@@ -10073,7 +10093,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>376</v>
       </c>
@@ -10108,7 +10128,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>380</v>
       </c>
@@ -10142,11 +10162,11 @@
       <c r="K93" s="1" t="s">
         <v>1413</v>
       </c>
-      <c r="M93" t="s">
+      <c r="N93" t="s">
         <v>1737</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>384</v>
       </c>
@@ -10181,7 +10201,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>388</v>
       </c>
@@ -10215,11 +10235,11 @@
       <c r="K95" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="M95" t="s">
+      <c r="N95" t="s">
         <v>1738</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>392</v>
       </c>
@@ -10253,11 +10273,11 @@
       <c r="K96" s="1" t="s">
         <v>1418</v>
       </c>
-      <c r="M96" t="s">
+      <c r="N96" t="s">
         <v>1739</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>396</v>
       </c>
@@ -10291,11 +10311,11 @@
       <c r="K97" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="M97" t="s">
+      <c r="N97" t="s">
         <v>1740</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>400</v>
       </c>
@@ -10330,7 +10350,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>404</v>
       </c>
@@ -10364,14 +10384,14 @@
       <c r="K99" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M99" t="s">
+      <c r="N99" t="s">
         <v>1741</v>
       </c>
-      <c r="O99" t="s">
+      <c r="P99" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>408</v>
       </c>
@@ -10405,11 +10425,11 @@
       <c r="K100" s="1" t="s">
         <v>1423</v>
       </c>
-      <c r="M100" t="s">
+      <c r="N100" t="s">
         <v>1742</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>412</v>
       </c>
@@ -10443,11 +10463,11 @@
       <c r="K101" s="1" t="s">
         <v>1425</v>
       </c>
-      <c r="O101" t="s">
+      <c r="P101" t="s">
         <v>1041</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>416</v>
       </c>
@@ -10481,11 +10501,11 @@
       <c r="K102" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="M102" t="s">
+      <c r="N102" t="s">
         <v>1743</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>420</v>
       </c>
@@ -10519,14 +10539,14 @@
       <c r="K103" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="M103" t="s">
+      <c r="N103" t="s">
         <v>1744</v>
       </c>
-      <c r="O103" t="s">
+      <c r="P103" t="s">
         <v>1948</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>425</v>
       </c>
@@ -10560,14 +10580,14 @@
       <c r="K104" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="M104" t="s">
+      <c r="N104" t="s">
         <v>1745</v>
       </c>
-      <c r="O104" t="s">
+      <c r="P104" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>429</v>
       </c>
@@ -10601,11 +10621,11 @@
       <c r="K105" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="M105" t="s">
+      <c r="N105" t="s">
         <v>1746</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>433</v>
       </c>
@@ -10639,11 +10659,11 @@
       <c r="K106" s="1" t="s">
         <v>1430</v>
       </c>
-      <c r="M106" t="s">
+      <c r="N106" t="s">
         <v>1747</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>437</v>
       </c>
@@ -10677,14 +10697,14 @@
       <c r="K107" s="1" t="s">
         <v>1431</v>
       </c>
-      <c r="M107" t="s">
+      <c r="N107" t="s">
         <v>1748</v>
       </c>
-      <c r="O107" t="s">
+      <c r="P107" t="s">
         <v>1949</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>441</v>
       </c>
@@ -10718,14 +10738,14 @@
       <c r="K108" s="1" t="s">
         <v>1433</v>
       </c>
-      <c r="M108" t="s">
+      <c r="N108" t="s">
         <v>1749</v>
       </c>
-      <c r="O108" t="s">
+      <c r="P108" t="s">
         <v>1950</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>445</v>
       </c>
@@ -10759,11 +10779,11 @@
       <c r="K109" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M109" t="s">
+      <c r="N109" t="s">
         <v>1750</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>449</v>
       </c>
@@ -10797,14 +10817,14 @@
       <c r="K110" s="1" t="s">
         <v>1366</v>
       </c>
-      <c r="M110" t="s">
+      <c r="N110" t="s">
         <v>1751</v>
       </c>
-      <c r="O110" t="s">
+      <c r="P110" t="s">
         <v>1951</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>451</v>
       </c>
@@ -10838,11 +10858,11 @@
       <c r="K111" s="1" t="s">
         <v>1437</v>
       </c>
-      <c r="M111" t="s">
+      <c r="N111" t="s">
         <v>1752</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>452</v>
       </c>
@@ -10873,11 +10893,11 @@
       <c r="J112" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="M112" t="s">
+      <c r="N112" t="s">
         <v>1753</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>456</v>
       </c>
@@ -10911,11 +10931,11 @@
       <c r="K113" s="1" t="s">
         <v>1439</v>
       </c>
-      <c r="M113" t="s">
+      <c r="N113" t="s">
         <v>1754</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>460</v>
       </c>
@@ -10943,11 +10963,11 @@
       <c r="J114" s="1" t="s">
         <v>1440</v>
       </c>
-      <c r="M114" t="s">
+      <c r="N114" t="s">
         <v>1755</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>464</v>
       </c>
@@ -10978,14 +10998,14 @@
       <c r="J115" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="L115" t="s">
+      <c r="M115" t="s">
         <v>2011</v>
       </c>
-      <c r="M115" t="s">
+      <c r="N115" t="s">
         <v>1756</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>468</v>
       </c>
@@ -11016,14 +11036,14 @@
       <c r="J116" s="1" t="s">
         <v>1442</v>
       </c>
-      <c r="L116" t="s">
+      <c r="M116" t="s">
         <v>27</v>
       </c>
-      <c r="M116" t="s">
+      <c r="N116" t="s">
         <v>1757</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>470</v>
       </c>
@@ -11054,14 +11074,14 @@
       <c r="J117" s="1" t="s">
         <v>1443</v>
       </c>
-      <c r="M117" t="s">
+      <c r="N117" t="s">
         <v>1758</v>
       </c>
-      <c r="O117" t="s">
+      <c r="P117" t="s">
         <v>1952</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>474</v>
       </c>
@@ -11092,11 +11112,11 @@
       <c r="J118" s="1" t="s">
         <v>1444</v>
       </c>
-      <c r="M118" t="s">
+      <c r="N118" t="s">
         <v>1759</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>478</v>
       </c>
@@ -11127,23 +11147,23 @@
       <c r="J119" s="1" t="s">
         <v>1445</v>
       </c>
-      <c r="M119" t="s">
+      <c r="N119" t="s">
         <v>1760</v>
       </c>
-      <c r="P119">
+      <c r="Q119">
         <v>1590102632</v>
       </c>
-      <c r="Q119">
+      <c r="R119">
         <v>1774134632</v>
       </c>
-      <c r="R119">
+      <c r="S119">
         <v>1726960232</v>
       </c>
-      <c r="S119">
+      <c r="T119">
         <v>53</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>483</v>
       </c>
@@ -11174,14 +11194,14 @@
       <c r="J120" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="M120" t="s">
+      <c r="N120" t="s">
         <v>1761</v>
       </c>
-      <c r="O120" t="s">
+      <c r="P120" t="s">
         <v>1953</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>487</v>
       </c>
@@ -11212,11 +11232,11 @@
       <c r="J121" s="1" t="s">
         <v>1446</v>
       </c>
-      <c r="M121" t="s">
+      <c r="N121" t="s">
         <v>1683</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>489</v>
       </c>
@@ -11248,7 +11268,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>493</v>
       </c>
@@ -11279,11 +11299,11 @@
       <c r="J123" s="1" t="s">
         <v>1441</v>
       </c>
-      <c r="M123" t="s">
+      <c r="N123" t="s">
         <v>1762</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>497</v>
       </c>
@@ -11314,11 +11334,11 @@
       <c r="J124" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O124" t="s">
+      <c r="P124" t="s">
         <v>1954</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>501</v>
       </c>
@@ -11349,14 +11369,14 @@
       <c r="J125" s="1" t="s">
         <v>1449</v>
       </c>
-      <c r="L125" t="s">
+      <c r="M125" t="s">
         <v>2003</v>
       </c>
-      <c r="M125" t="s">
+      <c r="N125" t="s">
         <v>1763</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>505</v>
       </c>
@@ -11387,11 +11407,11 @@
       <c r="J126" s="1" t="s">
         <v>1450</v>
       </c>
-      <c r="M126" t="s">
+      <c r="N126" t="s">
         <v>1764</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>509</v>
       </c>
@@ -11422,14 +11442,14 @@
       <c r="J127" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M127" t="s">
+      <c r="N127" t="s">
         <v>1765</v>
       </c>
-      <c r="O127" t="s">
+      <c r="P127" t="s">
         <v>1955</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>513</v>
       </c>
@@ -11460,14 +11480,14 @@
       <c r="J128" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="L128" t="s">
+      <c r="M128" t="s">
         <v>2012</v>
       </c>
-      <c r="M128" t="s">
+      <c r="N128" t="s">
         <v>1766</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>517</v>
       </c>
@@ -11498,11 +11518,11 @@
       <c r="J129" s="1" t="s">
         <v>1452</v>
       </c>
-      <c r="M129" t="s">
+      <c r="N129" t="s">
         <v>1767</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>521</v>
       </c>
@@ -11533,11 +11553,11 @@
       <c r="J130" s="1" t="s">
         <v>1454</v>
       </c>
-      <c r="M130" t="s">
+      <c r="N130" t="s">
         <v>1768</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>525</v>
       </c>
@@ -11568,11 +11588,11 @@
       <c r="J131" s="1" t="s">
         <v>1455</v>
       </c>
-      <c r="M131" t="s">
+      <c r="N131" t="s">
         <v>1769</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>529</v>
       </c>
@@ -11603,11 +11623,11 @@
       <c r="J132" s="1" t="s">
         <v>1456</v>
       </c>
-      <c r="M132" t="s">
+      <c r="N132" t="s">
         <v>1770</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>533</v>
       </c>
@@ -11638,11 +11658,11 @@
       <c r="J133" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M133" t="s">
+      <c r="N133" t="s">
         <v>1771</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>537</v>
       </c>
@@ -11673,14 +11693,14 @@
       <c r="J134" s="1" t="s">
         <v>1457</v>
       </c>
-      <c r="M134" t="s">
+      <c r="N134" t="s">
         <v>1772</v>
       </c>
-      <c r="N134">
+      <c r="O134">
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>541</v>
       </c>
@@ -11711,14 +11731,14 @@
       <c r="J135" s="1" t="s">
         <v>1458</v>
       </c>
-      <c r="M135" t="s">
+      <c r="N135" t="s">
         <v>1773</v>
       </c>
-      <c r="O135" t="s">
+      <c r="P135" t="s">
         <v>1956</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>545</v>
       </c>
@@ -11749,14 +11769,14 @@
       <c r="J136" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="M136" t="s">
+      <c r="N136" t="s">
         <v>1774</v>
       </c>
-      <c r="N136">
+      <c r="O136">
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>549</v>
       </c>
@@ -11787,11 +11807,11 @@
       <c r="J137" s="1" t="s">
         <v>1459</v>
       </c>
-      <c r="M137" t="s">
+      <c r="N137" t="s">
         <v>1775</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>553</v>
       </c>
@@ -11822,14 +11842,14 @@
       <c r="J138" s="1" t="s">
         <v>1461</v>
       </c>
-      <c r="M138" t="s">
+      <c r="N138" t="s">
         <v>1776</v>
       </c>
-      <c r="O138" t="s">
+      <c r="P138" t="s">
         <v>1957</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>557</v>
       </c>
@@ -11860,14 +11880,14 @@
       <c r="J139" s="1" t="s">
         <v>1378</v>
       </c>
-      <c r="L139" t="s">
+      <c r="M139" t="s">
         <v>2013</v>
       </c>
-      <c r="M139" t="s">
+      <c r="N139" t="s">
         <v>1777</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>559</v>
       </c>
@@ -11895,11 +11915,11 @@
       <c r="J140" s="1" t="s">
         <v>1462</v>
       </c>
-      <c r="O140" t="s">
+      <c r="P140" t="s">
         <v>1958</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>564</v>
       </c>
@@ -11927,14 +11947,14 @@
       <c r="J141" s="1" t="s">
         <v>1463</v>
       </c>
-      <c r="M141" t="s">
+      <c r="N141" t="s">
         <v>1778</v>
       </c>
-      <c r="O141" t="s">
+      <c r="P141" t="s">
         <v>1959</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>568</v>
       </c>
@@ -11962,14 +11982,14 @@
       <c r="J142" s="1" t="s">
         <v>1464</v>
       </c>
-      <c r="M142" t="s">
+      <c r="N142" t="s">
         <v>1779</v>
       </c>
-      <c r="O142" t="s">
+      <c r="P142" t="s">
         <v>1960</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>572</v>
       </c>
@@ -12000,11 +12020,11 @@
       <c r="J143" s="1" t="s">
         <v>1465</v>
       </c>
-      <c r="M143" t="s">
+      <c r="N143" t="s">
         <v>1780</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>575</v>
       </c>
@@ -12035,14 +12055,14 @@
       <c r="J144" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M144" t="s">
+      <c r="N144" t="s">
         <v>1727</v>
       </c>
-      <c r="O144" t="s">
+      <c r="P144" t="s">
         <v>1961</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>579</v>
       </c>
@@ -12073,11 +12093,11 @@
       <c r="J145" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="M145" t="s">
+      <c r="N145" t="s">
         <v>1781</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>583</v>
       </c>
@@ -12108,11 +12128,11 @@
       <c r="J146" s="1" t="s">
         <v>1466</v>
       </c>
-      <c r="M146" t="s">
+      <c r="N146" t="s">
         <v>1782</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>585</v>
       </c>
@@ -12143,11 +12163,11 @@
       <c r="J147" s="1" t="s">
         <v>1467</v>
       </c>
-      <c r="M147" t="s">
+      <c r="N147" t="s">
         <v>1765</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>589</v>
       </c>
@@ -12178,11 +12198,11 @@
       <c r="J148" s="1" t="s">
         <v>1334</v>
       </c>
-      <c r="M148" t="s">
+      <c r="N148" t="s">
         <v>1783</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>593</v>
       </c>
@@ -12213,11 +12233,11 @@
       <c r="J149" s="1" t="s">
         <v>1366</v>
       </c>
-      <c r="M149" t="s">
+      <c r="N149" t="s">
         <v>1784</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>597</v>
       </c>
@@ -12248,11 +12268,11 @@
       <c r="J150" s="1" t="s">
         <v>1376</v>
       </c>
-      <c r="M150" t="s">
+      <c r="N150" t="s">
         <v>1785</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>601</v>
       </c>
@@ -12283,11 +12303,11 @@
       <c r="J151" s="1" t="s">
         <v>1311</v>
       </c>
-      <c r="M151" t="s">
+      <c r="N151" t="s">
         <v>1786</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>605</v>
       </c>
@@ -12318,14 +12338,14 @@
       <c r="J152" s="1" t="s">
         <v>1374</v>
       </c>
-      <c r="M152" t="s">
+      <c r="N152" t="s">
         <v>1787</v>
       </c>
-      <c r="O152" t="s">
+      <c r="P152" t="s">
         <v>1962</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>609</v>
       </c>
@@ -12356,14 +12376,14 @@
       <c r="J153" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="M153" t="s">
+      <c r="N153" t="s">
         <v>1788</v>
       </c>
-      <c r="O153" t="s">
+      <c r="P153" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>613</v>
       </c>
@@ -12392,7 +12412,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>617</v>
       </c>
@@ -12423,14 +12443,14 @@
       <c r="J155" s="1" t="s">
         <v>1376</v>
       </c>
-      <c r="M155" t="s">
+      <c r="N155" t="s">
         <v>1789</v>
       </c>
-      <c r="O155" t="s">
+      <c r="P155" t="s">
         <v>1963</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>621</v>
       </c>
@@ -12461,11 +12481,11 @@
       <c r="J156" s="1" t="s">
         <v>1416</v>
       </c>
-      <c r="M156" t="s">
+      <c r="N156" t="s">
         <v>1790</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>625</v>
       </c>
@@ -12496,14 +12516,14 @@
       <c r="J157" s="1" t="s">
         <v>1459</v>
       </c>
-      <c r="M157" t="s">
+      <c r="N157" t="s">
         <v>1791</v>
       </c>
-      <c r="O157" t="s">
+      <c r="P157" t="s">
         <v>1964</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>629</v>
       </c>
@@ -12534,17 +12554,17 @@
       <c r="J158" s="1" t="s">
         <v>1470</v>
       </c>
-      <c r="L158" t="s">
+      <c r="M158" t="s">
         <v>29</v>
       </c>
-      <c r="M158" t="s">
+      <c r="N158" t="s">
         <v>1792</v>
       </c>
-      <c r="O158" t="s">
+      <c r="P158" t="s">
         <v>1965</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>633</v>
       </c>
@@ -12575,11 +12595,11 @@
       <c r="J159" s="1" t="s">
         <v>1388</v>
       </c>
-      <c r="M159" t="s">
+      <c r="N159" t="s">
         <v>1793</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>635</v>
       </c>
@@ -12611,7 +12631,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>638</v>
       </c>
@@ -12645,14 +12665,14 @@
       <c r="K161" s="1" t="s">
         <v>1473</v>
       </c>
-      <c r="L161" t="s">
+      <c r="M161" t="s">
         <v>2014</v>
       </c>
-      <c r="M161" t="s">
+      <c r="N161" t="s">
         <v>1794</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>640</v>
       </c>
@@ -12683,11 +12703,11 @@
       <c r="J162" s="1" t="s">
         <v>1376</v>
       </c>
-      <c r="M162" t="s">
+      <c r="N162" t="s">
         <v>1795</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>644</v>
       </c>
@@ -12721,11 +12741,11 @@
       <c r="K163" s="1" t="s">
         <v>1475</v>
       </c>
-      <c r="M163" t="s">
+      <c r="N163" t="s">
         <v>1796</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>648</v>
       </c>
@@ -12759,11 +12779,11 @@
       <c r="K164" s="1" t="s">
         <v>1435</v>
       </c>
-      <c r="M164" t="s">
+      <c r="N164" t="s">
         <v>1797</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>650</v>
       </c>
@@ -12794,11 +12814,11 @@
       <c r="K165" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="M165" t="s">
+      <c r="N165" t="s">
         <v>1798</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>652</v>
       </c>
@@ -12832,11 +12852,11 @@
       <c r="K166" s="1" t="s">
         <v>1479</v>
       </c>
-      <c r="M166" t="s">
+      <c r="N166" t="s">
         <v>1799</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>656</v>
       </c>
@@ -12870,14 +12890,14 @@
       <c r="K167" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M167" t="s">
+      <c r="N167" t="s">
         <v>1800</v>
       </c>
-      <c r="O167" t="s">
+      <c r="P167" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>660</v>
       </c>
@@ -12911,11 +12931,11 @@
       <c r="K168" s="1" t="s">
         <v>1482</v>
       </c>
-      <c r="M168" t="s">
+      <c r="N168" t="s">
         <v>1801</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>664</v>
       </c>
@@ -12949,14 +12969,14 @@
       <c r="K169" s="1" t="s">
         <v>1483</v>
       </c>
-      <c r="M169" t="s">
+      <c r="N169" t="s">
         <v>1802</v>
       </c>
-      <c r="O169" t="s">
+      <c r="P169" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>668</v>
       </c>
@@ -12990,14 +13010,14 @@
       <c r="K170" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="L170" t="s">
+      <c r="M170" t="s">
         <v>2015</v>
       </c>
-      <c r="M170" t="s">
+      <c r="N170" t="s">
         <v>1803</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>670</v>
       </c>
@@ -13031,11 +13051,11 @@
       <c r="K171" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M171" t="s">
+      <c r="N171" t="s">
         <v>1804</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>673</v>
       </c>
@@ -13069,11 +13089,11 @@
       <c r="K172" s="1" t="s">
         <v>1486</v>
       </c>
-      <c r="M172" t="s">
+      <c r="N172" t="s">
         <v>1805</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>677</v>
       </c>
@@ -13107,11 +13127,11 @@
       <c r="K173" s="1" t="s">
         <v>1372</v>
       </c>
-      <c r="M173" t="s">
+      <c r="N173" t="s">
         <v>1806</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>681</v>
       </c>
@@ -13145,11 +13165,11 @@
       <c r="K174" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O174" t="s">
+      <c r="P174" t="s">
         <v>1052</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>684</v>
       </c>
@@ -13183,11 +13203,11 @@
       <c r="K175" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M175" t="s">
+      <c r="N175" t="s">
         <v>1807</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>686</v>
       </c>
@@ -13221,14 +13241,14 @@
       <c r="K176" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L176" t="s">
+      <c r="M176" t="s">
         <v>2003</v>
       </c>
-      <c r="M176" t="s">
+      <c r="N176" t="s">
         <v>1808</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>690</v>
       </c>
@@ -13262,14 +13282,14 @@
       <c r="K177" s="1" t="s">
         <v>1491</v>
       </c>
-      <c r="M177" t="s">
+      <c r="N177" t="s">
         <v>1809</v>
       </c>
-      <c r="O177" t="s">
+      <c r="P177" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>694</v>
       </c>
@@ -13303,11 +13323,11 @@
       <c r="K178" s="1" t="s">
         <v>1460</v>
       </c>
-      <c r="O178" t="s">
+      <c r="P178" t="s">
         <v>1966</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>698</v>
       </c>
@@ -13338,14 +13358,14 @@
       <c r="K179" s="1" t="s">
         <v>1492</v>
       </c>
-      <c r="L179" t="s">
+      <c r="M179" t="s">
         <v>28</v>
       </c>
-      <c r="M179" t="s">
+      <c r="N179" t="s">
         <v>1810</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>702</v>
       </c>
@@ -13379,11 +13399,11 @@
       <c r="K180" s="1" t="s">
         <v>1494</v>
       </c>
-      <c r="M180" t="s">
+      <c r="N180" t="s">
         <v>1811</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>706</v>
       </c>
@@ -13414,11 +13434,11 @@
       <c r="J181" s="1" t="s">
         <v>1495</v>
       </c>
-      <c r="M181" t="s">
+      <c r="N181" t="s">
         <v>1812</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>710</v>
       </c>
@@ -13452,11 +13472,11 @@
       <c r="K182" s="1" t="s">
         <v>1497</v>
       </c>
-      <c r="M182" t="s">
+      <c r="N182" t="s">
         <v>1813</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>714</v>
       </c>
@@ -13490,11 +13510,11 @@
       <c r="K183" s="1" t="s">
         <v>1498</v>
       </c>
-      <c r="L183" t="s">
+      <c r="M183" t="s">
         <v>2016</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>718</v>
       </c>
@@ -13525,14 +13545,14 @@
       <c r="K184" s="1" t="s">
         <v>1499</v>
       </c>
-      <c r="L184" t="s">
+      <c r="M184" t="s">
         <v>29</v>
       </c>
-      <c r="M184" t="s">
+      <c r="N184" t="s">
         <v>1814</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>722</v>
       </c>
@@ -13566,11 +13586,11 @@
       <c r="K185" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M185" t="s">
+      <c r="N185" t="s">
         <v>1815</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>726</v>
       </c>
@@ -13604,11 +13624,11 @@
       <c r="K186" s="1" t="s">
         <v>1501</v>
       </c>
-      <c r="M186" t="s">
+      <c r="N186" t="s">
         <v>1816</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>730</v>
       </c>
@@ -13642,11 +13662,11 @@
       <c r="K187" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O187" t="s">
+      <c r="P187" t="s">
         <v>1967</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>734</v>
       </c>
@@ -13680,11 +13700,11 @@
       <c r="K188" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="M188" t="s">
+      <c r="N188" t="s">
         <v>1817</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>738</v>
       </c>
@@ -13718,11 +13738,11 @@
       <c r="K189" s="1" t="s">
         <v>1333</v>
       </c>
-      <c r="M189" t="s">
+      <c r="N189" t="s">
         <v>1818</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>742</v>
       </c>
@@ -13756,11 +13776,11 @@
       <c r="K190" s="1" t="s">
         <v>1504</v>
       </c>
-      <c r="M190" t="s">
+      <c r="N190" t="s">
         <v>1819</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>746</v>
       </c>
@@ -13795,7 +13815,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>750</v>
       </c>
@@ -13829,14 +13849,14 @@
       <c r="K192" s="1" t="s">
         <v>1507</v>
       </c>
-      <c r="L192" t="s">
+      <c r="M192" t="s">
         <v>30</v>
       </c>
-      <c r="M192" t="s">
+      <c r="N192" t="s">
         <v>1820</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>754</v>
       </c>
@@ -13871,7 +13891,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>758</v>
       </c>
@@ -13905,11 +13925,11 @@
       <c r="K194" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M194" t="s">
+      <c r="N194" t="s">
         <v>1821</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>762</v>
       </c>
@@ -13943,14 +13963,14 @@
       <c r="K195" s="1" t="s">
         <v>1512</v>
       </c>
-      <c r="L195" t="s">
+      <c r="M195" t="s">
         <v>29</v>
       </c>
-      <c r="M195" t="s">
+      <c r="N195" t="s">
         <v>1822</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>766</v>
       </c>
@@ -13984,11 +14004,11 @@
       <c r="K196" s="1" t="s">
         <v>1341</v>
       </c>
-      <c r="O196" t="s">
+      <c r="P196" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>770</v>
       </c>
@@ -14022,11 +14042,11 @@
       <c r="K197" s="1" t="s">
         <v>1514</v>
       </c>
-      <c r="M197" t="s">
+      <c r="N197" t="s">
         <v>1823</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>774</v>
       </c>
@@ -14060,11 +14080,11 @@
       <c r="K198" s="1" t="s">
         <v>1516</v>
       </c>
-      <c r="M198" t="s">
+      <c r="N198" t="s">
         <v>1824</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>778</v>
       </c>
@@ -14098,14 +14118,14 @@
       <c r="K199" s="1" t="s">
         <v>1517</v>
       </c>
-      <c r="M199" t="s">
+      <c r="N199" t="s">
         <v>1825</v>
       </c>
-      <c r="O199" t="s">
+      <c r="P199" t="s">
         <v>1968</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>782</v>
       </c>
@@ -14139,11 +14159,11 @@
       <c r="K200" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M200" t="s">
+      <c r="N200" t="s">
         <v>1826</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>786</v>
       </c>
@@ -14174,11 +14194,11 @@
       <c r="J201" s="1" t="s">
         <v>1344</v>
       </c>
-      <c r="M201" t="s">
+      <c r="N201" t="s">
         <v>1827</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>788</v>
       </c>
@@ -14209,17 +14229,17 @@
       <c r="J202" s="1" t="s">
         <v>1345</v>
       </c>
-      <c r="M202" t="s">
+      <c r="N202" t="s">
         <v>1828</v>
       </c>
-      <c r="N202">
+      <c r="O202">
         <v>1</v>
       </c>
-      <c r="O202" t="s">
+      <c r="P202" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>791</v>
       </c>
@@ -14250,14 +14270,14 @@
       <c r="J203" s="1" t="s">
         <v>1518</v>
       </c>
-      <c r="M203" t="s">
+      <c r="N203" t="s">
         <v>1829</v>
       </c>
-      <c r="N203">
+      <c r="O203">
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>793</v>
       </c>
@@ -14288,14 +14308,14 @@
       <c r="J204" s="1" t="s">
         <v>1519</v>
       </c>
-      <c r="L204" t="s">
+      <c r="M204" t="s">
         <v>2006</v>
       </c>
-      <c r="N204">
+      <c r="O204">
         <v>3</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>795</v>
       </c>
@@ -14326,14 +14346,14 @@
       <c r="J205" s="1" t="s">
         <v>1520</v>
       </c>
-      <c r="L205" t="s">
+      <c r="M205" t="s">
         <v>2004</v>
       </c>
-      <c r="M205" t="s">
+      <c r="N205" t="s">
         <v>1830</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>799</v>
       </c>
@@ -14364,14 +14384,14 @@
       <c r="J206" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M206" t="s">
+      <c r="N206" t="s">
         <v>1831</v>
       </c>
-      <c r="O206" t="s">
+      <c r="P206" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>803</v>
       </c>
@@ -14405,14 +14425,14 @@
       <c r="K207" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="L207" t="s">
+      <c r="M207" t="s">
         <v>2005</v>
       </c>
-      <c r="M207" t="s">
+      <c r="N207" t="s">
         <v>1832</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>807</v>
       </c>
@@ -14446,11 +14466,11 @@
       <c r="K208" s="1" t="s">
         <v>1521</v>
       </c>
-      <c r="M208" t="s">
+      <c r="N208" t="s">
         <v>1833</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>811</v>
       </c>
@@ -14484,11 +14504,11 @@
       <c r="K209" s="1" t="s">
         <v>1447</v>
       </c>
-      <c r="M209" t="s">
+      <c r="N209" t="s">
         <v>1834</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>815</v>
       </c>
@@ -14519,14 +14539,14 @@
       <c r="K210" s="1" t="s">
         <v>1524</v>
       </c>
-      <c r="M210" t="s">
+      <c r="N210" t="s">
         <v>1835</v>
       </c>
-      <c r="O210" t="s">
+      <c r="P210" t="s">
         <v>1969</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>819</v>
       </c>
@@ -14560,11 +14580,11 @@
       <c r="K211" s="1" t="s">
         <v>1292</v>
       </c>
-      <c r="M211" t="s">
+      <c r="N211" t="s">
         <v>1836</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>823</v>
       </c>
@@ -14596,7 +14616,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>827</v>
       </c>
@@ -14630,14 +14650,14 @@
       <c r="K213" s="1" t="s">
         <v>1527</v>
       </c>
-      <c r="M213" t="s">
+      <c r="N213" t="s">
         <v>1837</v>
       </c>
-      <c r="O213" t="s">
+      <c r="P213" t="s">
         <v>1970</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>831</v>
       </c>
@@ -14671,14 +14691,14 @@
       <c r="K214" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="L214" t="s">
+      <c r="M214" t="s">
         <v>28</v>
       </c>
-      <c r="M214" t="s">
+      <c r="N214" t="s">
         <v>1838</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>833</v>
       </c>
@@ -14712,14 +14732,14 @@
       <c r="K215" s="1" t="s">
         <v>1529</v>
       </c>
-      <c r="M215" t="s">
+      <c r="N215" t="s">
         <v>1839</v>
       </c>
-      <c r="O215" t="s">
+      <c r="P215" t="s">
         <v>1971</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>836</v>
       </c>
@@ -14753,14 +14773,14 @@
       <c r="K216" s="1" t="s">
         <v>1531</v>
       </c>
-      <c r="M216" t="s">
+      <c r="N216" t="s">
         <v>1840</v>
       </c>
-      <c r="O216" t="s">
+      <c r="P216" t="s">
         <v>1972</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>838</v>
       </c>
@@ -14794,17 +14814,17 @@
       <c r="K217" s="1" t="s">
         <v>1532</v>
       </c>
-      <c r="L217" t="s">
+      <c r="M217" t="s">
         <v>2008</v>
       </c>
-      <c r="M217" t="s">
+      <c r="N217" t="s">
         <v>1727</v>
       </c>
-      <c r="O217" t="s">
+      <c r="P217" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>842</v>
       </c>
@@ -14838,17 +14858,17 @@
       <c r="K218" s="1" t="s">
         <v>1534</v>
       </c>
-      <c r="L218" t="s">
+      <c r="M218" t="s">
         <v>2017</v>
       </c>
-      <c r="M218" t="s">
+      <c r="N218" t="s">
         <v>1841</v>
       </c>
-      <c r="O218" t="s">
+      <c r="P218" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>844</v>
       </c>
@@ -14882,14 +14902,14 @@
       <c r="K219" s="1" t="s">
         <v>1536</v>
       </c>
-      <c r="M219" t="s">
+      <c r="N219" t="s">
         <v>1735</v>
       </c>
-      <c r="O219" t="s">
+      <c r="P219" t="s">
         <v>1973</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>848</v>
       </c>
@@ -14923,11 +14943,11 @@
       <c r="K220" s="1" t="s">
         <v>1538</v>
       </c>
-      <c r="M220" t="s">
+      <c r="N220" t="s">
         <v>1842</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>852</v>
       </c>
@@ -14961,11 +14981,11 @@
       <c r="K221" s="1" t="s">
         <v>1540</v>
       </c>
-      <c r="M221" t="s">
+      <c r="N221" t="s">
         <v>1843</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>856</v>
       </c>
@@ -14999,11 +15019,11 @@
       <c r="K222" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M222" t="s">
+      <c r="N222" t="s">
         <v>1844</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>860</v>
       </c>
@@ -15037,17 +15057,17 @@
       <c r="K223" s="1" t="s">
         <v>1491</v>
       </c>
-      <c r="L223" t="s">
+      <c r="M223" t="s">
         <v>29</v>
       </c>
-      <c r="M223" t="s">
+      <c r="N223" t="s">
         <v>1845</v>
       </c>
-      <c r="O223" t="s">
+      <c r="P223" t="s">
         <v>1974</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>864</v>
       </c>
@@ -15081,11 +15101,11 @@
       <c r="K224" s="1" t="s">
         <v>1543</v>
       </c>
-      <c r="M224" t="s">
+      <c r="N224" t="s">
         <v>1846</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>868</v>
       </c>
@@ -15113,11 +15133,11 @@
       <c r="I225" t="s">
         <v>871</v>
       </c>
-      <c r="M225" t="s">
+      <c r="N225" t="s">
         <v>1847</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>872</v>
       </c>
@@ -15151,14 +15171,14 @@
       <c r="K226" s="1" t="s">
         <v>1544</v>
       </c>
-      <c r="L226" t="s">
+      <c r="M226" t="s">
         <v>29</v>
       </c>
-      <c r="M226" t="s">
+      <c r="N226" t="s">
         <v>1848</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>876</v>
       </c>
@@ -15192,11 +15212,11 @@
       <c r="K227" s="1" t="s">
         <v>1545</v>
       </c>
-      <c r="M227" t="s">
+      <c r="N227" t="s">
         <v>1849</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>878</v>
       </c>
@@ -15230,11 +15250,11 @@
       <c r="K228" s="1" t="s">
         <v>1333</v>
       </c>
-      <c r="M228" t="s">
+      <c r="N228" t="s">
         <v>1850</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>880</v>
       </c>
@@ -15268,14 +15288,14 @@
       <c r="K229" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="M229" t="s">
+      <c r="N229" t="s">
         <v>1851</v>
       </c>
-      <c r="O229" t="s">
+      <c r="P229" t="s">
         <v>1975</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>884</v>
       </c>
@@ -15309,14 +15329,14 @@
       <c r="K230" s="1" t="s">
         <v>1292</v>
       </c>
-      <c r="M230" t="s">
+      <c r="N230" t="s">
         <v>1852</v>
       </c>
-      <c r="O230" t="s">
+      <c r="P230" t="s">
         <v>1976</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>888</v>
       </c>
@@ -15350,11 +15370,11 @@
       <c r="K231" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M231" t="s">
+      <c r="N231" t="s">
         <v>1803</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>892</v>
       </c>
@@ -15388,11 +15408,11 @@
       <c r="K232" s="1" t="s">
         <v>1549</v>
       </c>
-      <c r="M232" t="s">
+      <c r="N232" t="s">
         <v>1853</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>896</v>
       </c>
@@ -15423,11 +15443,11 @@
       <c r="J233" s="1" t="s">
         <v>1550</v>
       </c>
-      <c r="M233" t="s">
+      <c r="N233" t="s">
         <v>1854</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>900</v>
       </c>
@@ -15461,14 +15481,14 @@
       <c r="K234" s="1" t="s">
         <v>1491</v>
       </c>
-      <c r="M234" t="s">
+      <c r="N234" t="s">
         <v>1855</v>
       </c>
-      <c r="O234" t="s">
+      <c r="P234" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>904</v>
       </c>
@@ -15502,11 +15522,11 @@
       <c r="K235" s="1" t="s">
         <v>1552</v>
       </c>
-      <c r="O235" t="s">
+      <c r="P235" t="s">
         <v>1977</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>908</v>
       </c>
@@ -15541,7 +15561,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>912</v>
       </c>
@@ -15575,11 +15595,11 @@
       <c r="K237" s="1" t="s">
         <v>1556</v>
       </c>
-      <c r="M237" t="s">
+      <c r="N237" t="s">
         <v>1856</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>916</v>
       </c>
@@ -15613,14 +15633,14 @@
       <c r="K238" s="1" t="s">
         <v>1292</v>
       </c>
-      <c r="L238" t="s">
+      <c r="M238" t="s">
         <v>2006</v>
       </c>
-      <c r="M238" t="s">
+      <c r="N238" t="s">
         <v>1857</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>920</v>
       </c>
@@ -15654,14 +15674,14 @@
       <c r="K239" s="1" t="s">
         <v>1558</v>
       </c>
-      <c r="M239" t="s">
+      <c r="N239" t="s">
         <v>1858</v>
       </c>
-      <c r="O239" t="s">
+      <c r="P239" t="s">
         <v>1978</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>924</v>
       </c>
@@ -15695,11 +15715,11 @@
       <c r="K240" s="1" t="s">
         <v>1559</v>
       </c>
-      <c r="M240" t="s">
+      <c r="N240" t="s">
         <v>1859</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>928</v>
       </c>
@@ -15733,14 +15753,14 @@
       <c r="K241" s="1" t="s">
         <v>1561</v>
       </c>
-      <c r="M241" t="s">
+      <c r="N241" t="s">
         <v>1860</v>
       </c>
-      <c r="O241" t="s">
+      <c r="P241" t="s">
         <v>1979</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>932</v>
       </c>
@@ -15774,11 +15794,11 @@
       <c r="K242" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M242" t="s">
+      <c r="N242" t="s">
         <v>1861</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>936</v>
       </c>
@@ -15812,14 +15832,14 @@
       <c r="K243" s="1" t="s">
         <v>1403</v>
       </c>
-      <c r="M243" t="s">
+      <c r="N243" t="s">
         <v>1862</v>
       </c>
-      <c r="O243" t="s">
+      <c r="P243" t="s">
         <v>1980</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>938</v>
       </c>
@@ -15853,11 +15873,11 @@
       <c r="K244" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="M244" t="s">
+      <c r="N244" t="s">
         <v>1863</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>943</v>
       </c>
@@ -15891,11 +15911,11 @@
       <c r="K245" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="N245">
+      <c r="O245">
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>945</v>
       </c>
@@ -15929,14 +15949,14 @@
       <c r="K246" s="1" t="s">
         <v>1311</v>
       </c>
-      <c r="M246" t="s">
+      <c r="N246" t="s">
         <v>1864</v>
       </c>
-      <c r="N246">
+      <c r="O246">
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>949</v>
       </c>
@@ -15970,11 +15990,11 @@
       <c r="K247" s="1" t="s">
         <v>1296</v>
       </c>
-      <c r="M247" t="s">
+      <c r="N247" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>953</v>
       </c>
@@ -16008,11 +16028,11 @@
       <c r="K248" s="1" t="s">
         <v>1565</v>
       </c>
-      <c r="M248" t="s">
+      <c r="N248" t="s">
         <v>1865</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>957</v>
       </c>
@@ -16046,11 +16066,11 @@
       <c r="K249" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="M249" t="s">
+      <c r="N249" t="s">
         <v>1866</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>961</v>
       </c>
@@ -16084,11 +16104,11 @@
       <c r="K250" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="M250" t="s">
+      <c r="N250" t="s">
         <v>1867</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>965</v>
       </c>
@@ -16122,11 +16142,11 @@
       <c r="K251" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O251" t="s">
+      <c r="P251" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>969</v>
       </c>
@@ -16160,11 +16180,11 @@
       <c r="K252" s="1" t="s">
         <v>1435</v>
       </c>
-      <c r="M252" t="s">
+      <c r="N252" t="s">
         <v>1868</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>973</v>
       </c>
@@ -16198,11 +16218,11 @@
       <c r="K253" s="1" t="s">
         <v>1569</v>
       </c>
-      <c r="M253" t="s">
+      <c r="N253" t="s">
         <v>1869</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>977</v>
       </c>
@@ -16233,11 +16253,11 @@
       <c r="J254" s="1" t="s">
         <v>1570</v>
       </c>
-      <c r="M254" t="s">
+      <c r="N254" t="s">
         <v>1870</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>981</v>
       </c>
@@ -16269,7 +16289,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>985</v>
       </c>
@@ -16300,11 +16320,11 @@
       <c r="J256" s="1" t="s">
         <v>1572</v>
       </c>
-      <c r="M256" t="s">
+      <c r="N256" t="s">
         <v>1871</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>989</v>
       </c>
@@ -16338,11 +16358,11 @@
       <c r="K257" s="1" t="s">
         <v>1573</v>
       </c>
-      <c r="M257" t="s">
+      <c r="N257" t="s">
         <v>1872</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>993</v>
       </c>
@@ -16376,11 +16396,11 @@
       <c r="K258" s="1" t="s">
         <v>1575</v>
       </c>
-      <c r="M258" t="s">
+      <c r="N258" t="s">
         <v>1873</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>995</v>
       </c>
@@ -16414,11 +16434,11 @@
       <c r="K259" s="1" t="s">
         <v>1460</v>
       </c>
-      <c r="M259" t="s">
+      <c r="N259" t="s">
         <v>1675</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>998</v>
       </c>
@@ -16452,11 +16472,11 @@
       <c r="K260" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M260" t="s">
+      <c r="N260" t="s">
         <v>1874</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>1000</v>
       </c>
@@ -16490,14 +16510,14 @@
       <c r="K261" s="1" t="s">
         <v>1578</v>
       </c>
-      <c r="L261" t="s">
+      <c r="M261" t="s">
         <v>2003</v>
       </c>
-      <c r="M261" t="s">
+      <c r="N261" t="s">
         <v>1875</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>1001</v>
       </c>
@@ -16532,7 +16552,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>1005</v>
       </c>
@@ -16566,14 +16586,14 @@
       <c r="K263" s="1" t="s">
         <v>1581</v>
       </c>
-      <c r="M263" t="s">
+      <c r="N263" t="s">
         <v>1685</v>
       </c>
-      <c r="O263" t="s">
+      <c r="P263" t="s">
         <v>1981</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>1009</v>
       </c>
@@ -16607,14 +16627,14 @@
       <c r="K264" s="1" t="s">
         <v>1274</v>
       </c>
-      <c r="L264" t="s">
+      <c r="M264" t="s">
         <v>27</v>
       </c>
-      <c r="M264" t="s">
+      <c r="N264" t="s">
         <v>1876</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>1013</v>
       </c>
@@ -16648,14 +16668,14 @@
       <c r="K265" s="1" t="s">
         <v>1583</v>
       </c>
-      <c r="L265" t="s">
+      <c r="M265" t="s">
         <v>2006</v>
       </c>
-      <c r="O265" t="s">
+      <c r="P265" t="s">
         <v>1982</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>1016</v>
       </c>
@@ -16689,14 +16709,14 @@
       <c r="K266" s="1" t="s">
         <v>1281</v>
       </c>
-      <c r="M266" t="s">
+      <c r="N266" t="s">
         <v>1877</v>
       </c>
-      <c r="O266" t="s">
+      <c r="P266" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>1020</v>
       </c>
@@ -16730,11 +16750,11 @@
       <c r="K267" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="M267" t="s">
+      <c r="N267" t="s">
         <v>1878</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>1024</v>
       </c>
@@ -16768,11 +16788,11 @@
       <c r="K268" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="M268" t="s">
+      <c r="N268" t="s">
         <v>1879</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>1028</v>
       </c>
@@ -16806,14 +16826,14 @@
       <c r="K269" s="1" t="s">
         <v>1587</v>
       </c>
-      <c r="M269" t="s">
+      <c r="N269" t="s">
         <v>1880</v>
       </c>
-      <c r="O269" t="s">
+      <c r="P269" t="s">
         <v>1983</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>1029</v>
       </c>
@@ -16847,14 +16867,14 @@
       <c r="K270" s="1" t="s">
         <v>1589</v>
       </c>
-      <c r="L270" t="s">
+      <c r="M270" t="s">
         <v>2018</v>
       </c>
-      <c r="M270" t="s">
+      <c r="N270" t="s">
         <v>1881</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>1031</v>
       </c>
@@ -16888,11 +16908,11 @@
       <c r="K271" s="1" t="s">
         <v>1590</v>
       </c>
-      <c r="M271" t="s">
+      <c r="N271" t="s">
         <v>1882</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>1033</v>
       </c>
@@ -16926,11 +16946,11 @@
       <c r="K272" s="1" t="s">
         <v>1591</v>
       </c>
-      <c r="M272" t="s">
+      <c r="N272" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>1035</v>
       </c>
@@ -16964,14 +16984,14 @@
       <c r="K273" s="1" t="s">
         <v>1388</v>
       </c>
-      <c r="L273" t="s">
+      <c r="M273" t="s">
         <v>28</v>
       </c>
-      <c r="M273" t="s">
+      <c r="N273" t="s">
         <v>1727</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>1037</v>
       </c>
@@ -17005,14 +17025,14 @@
       <c r="K274" s="1" t="s">
         <v>1593</v>
       </c>
-      <c r="M274" t="s">
+      <c r="N274" t="s">
         <v>1884</v>
       </c>
-      <c r="O274" t="s">
+      <c r="P274" t="s">
         <v>1984</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>1041</v>
       </c>
@@ -17046,11 +17066,11 @@
       <c r="K275" s="1" t="s">
         <v>1595</v>
       </c>
-      <c r="M275" t="s">
+      <c r="N275" t="s">
         <v>1885</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>1044</v>
       </c>
@@ -17084,11 +17104,11 @@
       <c r="K276" s="1" t="s">
         <v>1596</v>
       </c>
-      <c r="M276" t="s">
+      <c r="N276" t="s">
         <v>1886</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>1048</v>
       </c>
@@ -17123,7 +17143,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>1052</v>
       </c>
@@ -17157,14 +17177,14 @@
       <c r="K278" s="1" t="s">
         <v>1598</v>
       </c>
-      <c r="M278" t="s">
+      <c r="N278" t="s">
         <v>1887</v>
       </c>
-      <c r="O278" t="s">
+      <c r="P278" t="s">
         <v>1985</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>1055</v>
       </c>
@@ -17198,11 +17218,11 @@
       <c r="K279" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="M279" t="s">
+      <c r="N279" t="s">
         <v>1888</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>1057</v>
       </c>
@@ -17237,7 +17257,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>1061</v>
       </c>
@@ -17272,7 +17292,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>1065</v>
       </c>
@@ -17306,11 +17326,11 @@
       <c r="K282" s="1" t="s">
         <v>1448</v>
       </c>
-      <c r="O282" t="s">
+      <c r="P282" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>1069</v>
       </c>
@@ -17344,11 +17364,11 @@
       <c r="K283" s="1" t="s">
         <v>1600</v>
       </c>
-      <c r="M283" t="s">
+      <c r="N283" t="s">
         <v>1889</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>1073</v>
       </c>
@@ -17382,11 +17402,11 @@
       <c r="K284" s="1" t="s">
         <v>1469</v>
       </c>
-      <c r="M284" t="s">
+      <c r="N284" t="s">
         <v>1890</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>1077</v>
       </c>
@@ -17420,14 +17440,14 @@
       <c r="K285" s="1" t="s">
         <v>1601</v>
       </c>
-      <c r="L285" t="s">
+      <c r="M285" t="s">
         <v>2006</v>
       </c>
-      <c r="M285" t="s">
+      <c r="N285" t="s">
         <v>1891</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>1081</v>
       </c>
@@ -17462,7 +17482,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>1085</v>
       </c>
@@ -17496,11 +17516,11 @@
       <c r="K287" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M287" t="s">
+      <c r="N287" t="s">
         <v>1892</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>1089</v>
       </c>
@@ -17535,7 +17555,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>1093</v>
       </c>
@@ -17569,11 +17589,11 @@
       <c r="K289" s="1" t="s">
         <v>1372</v>
       </c>
-      <c r="M289" t="s">
+      <c r="N289" t="s">
         <v>1893</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>1097</v>
       </c>
@@ -17607,11 +17627,11 @@
       <c r="K290" s="1" t="s">
         <v>1605</v>
       </c>
-      <c r="M290" t="s">
+      <c r="N290" t="s">
         <v>1894</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>1101</v>
       </c>
@@ -17645,14 +17665,14 @@
       <c r="K291" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="L291" t="s">
+      <c r="M291" t="s">
         <v>30</v>
       </c>
-      <c r="M291" t="s">
+      <c r="N291" t="s">
         <v>1895</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>1105</v>
       </c>
@@ -17686,14 +17706,14 @@
       <c r="K292" s="1" t="s">
         <v>1606</v>
       </c>
-      <c r="M292" t="s">
+      <c r="N292" t="s">
         <v>1896</v>
       </c>
-      <c r="O292" t="s">
+      <c r="P292" t="s">
         <v>1986</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>1109</v>
       </c>
@@ -17727,11 +17747,11 @@
       <c r="K293" s="1" t="s">
         <v>1607</v>
       </c>
-      <c r="M293" t="s">
+      <c r="N293" t="s">
         <v>1897</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>1113</v>
       </c>
@@ -17765,11 +17785,11 @@
       <c r="K294" s="1" t="s">
         <v>1608</v>
       </c>
-      <c r="O294" t="s">
+      <c r="P294" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>1117</v>
       </c>
@@ -17803,11 +17823,11 @@
       <c r="K295" s="1" t="s">
         <v>1609</v>
       </c>
-      <c r="M295" t="s">
+      <c r="N295" t="s">
         <v>1898</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>1121</v>
       </c>
@@ -17841,14 +17861,14 @@
       <c r="K296" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="M296" t="s">
+      <c r="N296" t="s">
         <v>1899</v>
       </c>
-      <c r="O296" t="s">
+      <c r="P296" t="s">
         <v>1987</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>1124</v>
       </c>
@@ -17876,11 +17896,11 @@
       <c r="I297" t="s">
         <v>1127</v>
       </c>
-      <c r="M297" t="s">
+      <c r="N297" t="s">
         <v>1900</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>1128</v>
       </c>
@@ -17914,11 +17934,11 @@
       <c r="K298" s="1" t="s">
         <v>1505</v>
       </c>
-      <c r="M298" t="s">
+      <c r="N298" t="s">
         <v>1901</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>1132</v>
       </c>
@@ -17953,7 +17973,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>1135</v>
       </c>
@@ -17987,11 +18007,11 @@
       <c r="K300" s="1" t="s">
         <v>1613</v>
       </c>
-      <c r="M300" t="s">
+      <c r="N300" t="s">
         <v>1902</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>1139</v>
       </c>
@@ -18026,7 +18046,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>1143</v>
       </c>
@@ -18054,11 +18074,11 @@
       <c r="I302" t="s">
         <v>1146</v>
       </c>
-      <c r="M302" t="s">
+      <c r="N302" t="s">
         <v>1903</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>1147</v>
       </c>
@@ -18092,11 +18112,11 @@
       <c r="K303" s="1" t="s">
         <v>1374</v>
       </c>
-      <c r="M303" t="s">
+      <c r="N303" t="s">
         <v>1904</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>1151</v>
       </c>
@@ -18130,14 +18150,14 @@
       <c r="K304" s="1" t="s">
         <v>1617</v>
       </c>
-      <c r="M304" t="s">
+      <c r="N304" t="s">
         <v>1905</v>
       </c>
-      <c r="O304" t="s">
+      <c r="P304" t="s">
         <v>1988</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>1155</v>
       </c>
@@ -18171,11 +18191,11 @@
       <c r="K305" s="1" t="s">
         <v>1618</v>
       </c>
-      <c r="M305" t="s">
+      <c r="N305" t="s">
         <v>1906</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>1159</v>
       </c>
@@ -18209,11 +18229,11 @@
       <c r="K306" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M306" t="s">
+      <c r="N306" t="s">
         <v>1673</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>1163</v>
       </c>
@@ -18247,11 +18267,11 @@
       <c r="K307" s="1" t="s">
         <v>1538</v>
       </c>
-      <c r="L307" t="s">
+      <c r="M307" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>1167</v>
       </c>
@@ -18285,11 +18305,11 @@
       <c r="K308" s="1" t="s">
         <v>1304</v>
       </c>
-      <c r="M308" t="s">
+      <c r="N308" t="s">
         <v>1907</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>1171</v>
       </c>
@@ -18323,11 +18343,11 @@
       <c r="K309" s="1" t="s">
         <v>1620</v>
       </c>
-      <c r="M309" t="s">
+      <c r="N309" t="s">
         <v>1675</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>1173</v>
       </c>
@@ -18361,11 +18381,11 @@
       <c r="K310" s="1" t="s">
         <v>1622</v>
       </c>
-      <c r="M310" t="s">
+      <c r="N310" t="s">
         <v>1908</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>1176</v>
       </c>
@@ -18399,11 +18419,11 @@
       <c r="K311" s="1" t="s">
         <v>1624</v>
       </c>
-      <c r="M311" t="s">
+      <c r="N311" t="s">
         <v>1909</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>1180</v>
       </c>
@@ -18437,14 +18457,14 @@
       <c r="K312" s="1" t="s">
         <v>1626</v>
       </c>
-      <c r="L312" t="s">
+      <c r="M312" t="s">
         <v>2003</v>
       </c>
-      <c r="M312" t="s">
+      <c r="N312" t="s">
         <v>1910</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>1182</v>
       </c>
@@ -18478,14 +18498,14 @@
       <c r="K313" s="1" t="s">
         <v>1341</v>
       </c>
-      <c r="M313" t="s">
+      <c r="N313" t="s">
         <v>1911</v>
       </c>
-      <c r="O313" t="s">
+      <c r="P313" t="s">
         <v>1989</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>1184</v>
       </c>
@@ -18519,14 +18539,14 @@
       <c r="K314" s="1" t="s">
         <v>1629</v>
       </c>
-      <c r="L314" t="s">
+      <c r="M314" t="s">
         <v>2004</v>
       </c>
-      <c r="M314" t="s">
+      <c r="N314" t="s">
         <v>1912</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>1186</v>
       </c>
@@ -18560,11 +18580,11 @@
       <c r="K315" s="1" t="s">
         <v>1631</v>
       </c>
-      <c r="M315" t="s">
+      <c r="N315" t="s">
         <v>1913</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>1187</v>
       </c>
@@ -18598,14 +18618,14 @@
       <c r="K316" s="1" t="s">
         <v>1410</v>
       </c>
-      <c r="M316" t="s">
+      <c r="N316" t="s">
         <v>1914</v>
       </c>
-      <c r="O316" t="s">
+      <c r="P316" t="s">
         <v>1990</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>1189</v>
       </c>
@@ -18639,14 +18659,14 @@
       <c r="K317" s="1" t="s">
         <v>1633</v>
       </c>
-      <c r="M317" t="s">
+      <c r="N317" t="s">
         <v>1835</v>
       </c>
-      <c r="O317" t="s">
+      <c r="P317" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>1191</v>
       </c>
@@ -18677,11 +18697,11 @@
       <c r="J318" s="1" t="s">
         <v>1634</v>
       </c>
-      <c r="M318" t="s">
+      <c r="N318" t="s">
         <v>1915</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>1194</v>
       </c>
@@ -18716,7 +18736,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>1198</v>
       </c>
@@ -18750,14 +18770,14 @@
       <c r="K320" s="1" t="s">
         <v>1636</v>
       </c>
-      <c r="M320" t="s">
+      <c r="N320" t="s">
         <v>1916</v>
       </c>
-      <c r="O320" t="s">
+      <c r="P320" t="s">
         <v>1991</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>1200</v>
       </c>
@@ -18791,11 +18811,11 @@
       <c r="K321" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="M321" t="s">
+      <c r="N321" t="s">
         <v>1864</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>1204</v>
       </c>
@@ -18826,11 +18846,11 @@
       <c r="J322" s="1" t="s">
         <v>1637</v>
       </c>
-      <c r="M322" t="s">
+      <c r="N322" t="s">
         <v>1917</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>1208</v>
       </c>
@@ -18861,11 +18881,11 @@
       <c r="J323" s="1" t="s">
         <v>1447</v>
       </c>
-      <c r="M323" t="s">
+      <c r="N323" t="s">
         <v>1685</v>
       </c>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>1211</v>
       </c>
@@ -18899,17 +18919,17 @@
       <c r="K324" s="1" t="s">
         <v>1589</v>
       </c>
-      <c r="L324" t="s">
+      <c r="M324" t="s">
         <v>2019</v>
       </c>
-      <c r="M324" t="s">
+      <c r="N324" t="s">
         <v>1918</v>
       </c>
-      <c r="O324" t="s">
+      <c r="P324" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>1213</v>
       </c>
@@ -18943,14 +18963,14 @@
       <c r="K325" s="1" t="s">
         <v>1639</v>
       </c>
-      <c r="M325" t="s">
+      <c r="N325" t="s">
         <v>1919</v>
       </c>
-      <c r="O325" t="s">
+      <c r="P325" t="s">
         <v>1992</v>
       </c>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>1217</v>
       </c>
@@ -18984,14 +19004,14 @@
       <c r="K326" s="1" t="s">
         <v>1641</v>
       </c>
-      <c r="M326" t="s">
+      <c r="N326" t="s">
         <v>1920</v>
       </c>
-      <c r="O326" t="s">
+      <c r="P326" t="s">
         <v>1993</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>1221</v>
       </c>
@@ -19022,14 +19042,14 @@
       <c r="J327" s="1" t="s">
         <v>1642</v>
       </c>
-      <c r="M327" t="s">
+      <c r="N327" t="s">
         <v>1921</v>
       </c>
-      <c r="O327" t="s">
+      <c r="P327" t="s">
         <v>1994</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>1225</v>
       </c>
@@ -19057,14 +19077,14 @@
       <c r="I328" t="s">
         <v>1228</v>
       </c>
-      <c r="M328" t="s">
+      <c r="N328" t="s">
         <v>1735</v>
       </c>
-      <c r="O328" t="s">
+      <c r="P328" t="s">
         <v>1995</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>1229</v>
       </c>
@@ -19098,14 +19118,14 @@
       <c r="K329" s="1" t="s">
         <v>1644</v>
       </c>
-      <c r="M329" t="s">
+      <c r="N329" t="s">
         <v>1922</v>
       </c>
-      <c r="O329" t="s">
+      <c r="P329" t="s">
         <v>1996</v>
       </c>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>1233</v>
       </c>
@@ -19139,11 +19159,11 @@
       <c r="K330" s="1" t="s">
         <v>1645</v>
       </c>
-      <c r="M330" t="s">
+      <c r="N330" t="s">
         <v>1923</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>1237</v>
       </c>
@@ -19177,11 +19197,11 @@
       <c r="K331" s="1" t="s">
         <v>1647</v>
       </c>
-      <c r="M331" t="s">
+      <c r="N331" t="s">
         <v>1924</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>1239</v>
       </c>
@@ -19215,14 +19235,14 @@
       <c r="K332" s="1" t="s">
         <v>1333</v>
       </c>
-      <c r="M332" t="s">
+      <c r="N332" t="s">
         <v>1925</v>
       </c>
-      <c r="O332" t="s">
+      <c r="P332" t="s">
         <v>1997</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>1243</v>
       </c>
@@ -19256,11 +19276,11 @@
       <c r="K333" s="1" t="s">
         <v>1649</v>
       </c>
-      <c r="M333" t="s">
+      <c r="N333" t="s">
         <v>1851</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>1247</v>
       </c>
@@ -19294,11 +19314,11 @@
       <c r="K334" s="1" t="s">
         <v>1650</v>
       </c>
-      <c r="M334" t="s">
+      <c r="N334" t="s">
         <v>1926</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>1251</v>
       </c>
@@ -19329,11 +19349,11 @@
       <c r="J335" s="1" t="s">
         <v>1651</v>
       </c>
-      <c r="M335" t="s">
+      <c r="N335" t="s">
         <v>1927</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>1255</v>
       </c>
@@ -19367,11 +19387,11 @@
       <c r="K336" s="1" t="s">
         <v>1462</v>
       </c>
-      <c r="M336" t="s">
+      <c r="N336" t="s">
         <v>1928</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>1257</v>
       </c>
@@ -19405,11 +19425,11 @@
       <c r="K337" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="M337" t="s">
+      <c r="N337" t="s">
         <v>1929</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>1259</v>
       </c>
@@ -19443,14 +19463,14 @@
       <c r="K338" s="1" t="s">
         <v>1654</v>
       </c>
-      <c r="M338" t="s">
+      <c r="N338" t="s">
         <v>1930</v>
       </c>
-      <c r="O338" t="s">
+      <c r="P338" t="s">
         <v>1998</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>1261</v>
       </c>
@@ -19484,11 +19504,11 @@
       <c r="K339" s="1" t="s">
         <v>1656</v>
       </c>
-      <c r="M339" t="s">
+      <c r="N339" t="s">
         <v>1931</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>1262</v>
       </c>
@@ -19522,14 +19542,14 @@
       <c r="K340" s="1" t="s">
         <v>1658</v>
       </c>
-      <c r="M340" t="s">
+      <c r="N340" t="s">
         <v>1862</v>
       </c>
-      <c r="O340" t="s">
+      <c r="P340" t="s">
         <v>1999</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>1264</v>
       </c>
@@ -19563,11 +19583,11 @@
       <c r="K341" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M341" t="s">
+      <c r="N341" t="s">
         <v>1932</v>
       </c>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>1267</v>
       </c>
@@ -19601,11 +19621,11 @@
       <c r="K342" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M342" t="s">
+      <c r="N342" t="s">
         <v>1933</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>1268</v>
       </c>
@@ -19639,10 +19659,10 @@
       <c r="K343" s="1" t="s">
         <v>1662</v>
       </c>
-      <c r="M343" t="s">
+      <c r="N343" t="s">
         <v>1934</v>
       </c>
-      <c r="O343" t="s">
+      <c r="P343" t="s">
         <v>838</v>
       </c>
     </row>

--- a/public/data/db-source/variable.xlsx
+++ b/public/data/db-source/variable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bassim/code/datannur/datannur_dev/public/data/db-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34178825-C5D0-5B4A-9A70-24018A376B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E960C8C-6BE6-3748-BBA7-58FF6896E4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3106" uniqueCount="2028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3107" uniqueCount="2029">
   <si>
     <t>id</t>
   </si>
@@ -6104,6 +6104,9 @@
   </si>
   <si>
     <t>pop_region__regionfake</t>
+  </si>
+  <si>
+    <t>is_pattern</t>
   </si>
 </sst>
 </file>
@@ -6177,9 +6180,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B5F79C97-E8B2-3E4B-873D-A9EBE7FF4B08}" name="Tableau1" displayName="Tableau1" ref="A1:T343" totalsRowShown="0">
-  <autoFilter ref="A1:T343" xr:uid="{B5F79C97-E8B2-3E4B-873D-A9EBE7FF4B08}"/>
-  <tableColumns count="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B5F79C97-E8B2-3E4B-873D-A9EBE7FF4B08}" name="Tableau1" displayName="Tableau1" ref="A1:U343" totalsRowShown="0">
+  <autoFilter ref="A1:U343" xr:uid="{B5F79C97-E8B2-3E4B-873D-A9EBE7FF4B08}"/>
+  <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{93604F40-CD55-3D4B-AC71-27C6EBB96585}" name="id"/>
     <tableColumn id="2" xr3:uid="{BF843A60-41B0-EA48-977A-51FEEA73F6C7}" name="dataset_id"/>
     <tableColumn id="3" xr3:uid="{BCB7C440-426C-EF4D-8E48-57BB86725760}" name="name"/>
@@ -6200,6 +6203,7 @@
     <tableColumn id="17" xr3:uid="{0AEBB360-9070-7B43-9CA7-884E075866BF}" name="max"/>
     <tableColumn id="18" xr3:uid="{C77E4BF0-5715-E048-A147-739835ABF606}" name="mean"/>
     <tableColumn id="19" xr3:uid="{DCF9CF32-8576-DF40-8B35-DAF22D9C2690}" name="std"/>
+    <tableColumn id="21" xr3:uid="{783800C0-D4F8-2742-A815-0D0E9C4DD42C}" name="is_pattern"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6492,7 +6496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T343"/>
+  <dimension ref="A1:U343"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
@@ -6512,7 +6516,7 @@
     <col min="16" max="16" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6573,8 +6577,11 @@
       <c r="T1" t="s">
         <v>2023</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U1" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -6615,7 +6622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -6656,7 +6663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -6697,7 +6704,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -6735,7 +6742,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -6776,7 +6783,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>56</v>
       </c>
@@ -6814,7 +6821,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -6852,7 +6859,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>64</v>
       </c>
@@ -6890,7 +6897,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>68</v>
       </c>
@@ -6934,7 +6941,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>72</v>
       </c>
@@ -6975,7 +6982,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>76</v>
       </c>
@@ -7013,7 +7020,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>80</v>
       </c>
@@ -7051,7 +7058,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>84</v>
       </c>
@@ -7092,7 +7099,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>88</v>
       </c>
@@ -7127,7 +7134,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>92</v>
       </c>
@@ -18157,7 +18164,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>1155</v>
       </c>
@@ -18195,7 +18202,7 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>1159</v>
       </c>
@@ -18233,7 +18240,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>1163</v>
       </c>
@@ -18271,7 +18278,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>1167</v>
       </c>
@@ -18309,7 +18316,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>1171</v>
       </c>
@@ -18347,7 +18354,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>1173</v>
       </c>
@@ -18385,7 +18392,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>1176</v>
       </c>
@@ -18423,7 +18430,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>1180</v>
       </c>
@@ -18464,7 +18471,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>1182</v>
       </c>
@@ -18504,8 +18511,11 @@
       <c r="P313" t="s">
         <v>1989</v>
       </c>
-    </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="U313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>1184</v>
       </c>
@@ -18546,7 +18556,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="315" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>1186</v>
       </c>
@@ -18584,7 +18594,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>1187</v>
       </c>
@@ -18625,7 +18635,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>1189</v>
       </c>
@@ -18666,7 +18676,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>1191</v>
       </c>
@@ -18701,7 +18711,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>1194</v>
       </c>
@@ -18736,7 +18746,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>1198</v>
       </c>
